--- a/analitika/ca-i-produkty.xlsx
+++ b/analitika/ca-i-produkty.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Барьеры" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Сообщения" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Продукты (глубина)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Смыслы (позже)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Смыслы" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Анкета (черновик)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Данные (что проверить)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="9">
@@ -160,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -204,6 +210,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1706,57 +1718,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Распаковка смыслов под продукт — боль/страх/возражение → аргумент (ШАБЛОН)</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Распаковка смыслов: боль/страх/возражение → аргумент через механику Виолы (язык из комментариев, партии 1–3)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Продукт</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Сегмент/угол</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Тип (боль/желание/страх/возражение)</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>Формулировка аудитории (её язык)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>Формулировка аудитории (её язык, из комментариев)</t>
+        </is>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Аргумент через продукт (смысл)</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Механика Виолы (источник)</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>Чего НЕ говорить</t>
         </is>
@@ -1765,7 +1777,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Событие 1990</t>
+          <t>Лид-магнит</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1775,99 +1787,358 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Страх</t>
+          <t>Боль</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>«Перестану помогать — стану плохой»</t>
+          <t>«Не могу отказать; отказ адресуй тем, кто относится потребительски»</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Роль ≠ ты. Можно быть плохим водителем и хорошим человеком; отказ не отменяет, что ты хороший.</t>
+          <t>Отказать — это вернуть чужое адресату, а не стать плохим</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Т5 сепарация от роли, «мне можно быть собой» (kanon §7)</t>
+          <t>Т2 «чужое вернуть адресату» (kanon §7)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>«Полюби себя» лозунгом</t>
+          <t>«просто уйди»</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Событие 1990</t>
+          <t>Лид-магнит</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>С1</t>
+          <t>С3</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Возражение</t>
+          <t>Желание</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>«У меня особый случай, уйти не могу»</t>
+          <t>«Надо научиться любить и думать прежде всего о себе»</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Программа не требует разрыва: контакт сохраняется, меняется твоё положение внутри него.</t>
+          <t>«Мне можно» — право выбрать себя вместо «я должна»</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Т6 «Белый халат», баланс даже с токсиками (kanon §8.1, §9)</t>
+          <t>Т3 «должна→могу», «мне можно выбирать себя» (kanon §7)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>«Просто уйдите»</t>
+          <t>«полюби себя» лозунгом</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>[ЗАПОЛНЯЕМ ПОЗЖЕ]</t>
+          <t>Лид-магнит</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>С3</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Страх</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>«Перестану помогать — стану плохой»</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Роль ≠ ты: можно быть плохим водителем и хорошим человеком</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Т4 сепарация от роли (kanon §7)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>«поставь границы» лозунгом</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Событие 1990</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>С1</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Возражение</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>«У меня особый случай, уйти не могу»</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Программа не требует разрыва: контакт сохраняется, меняется твоё положение</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Т6 «Белый халат» (kanon §8.1, §9)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>«прекрати общение»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Флагман</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>С5</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Страх</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>«Сорвалась — значит безвольная»</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Срыв — часть процесса, а не доказательство испорченности</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Т7, письмо себе (kanon §8.2)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>«зависимость» в заголовке</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Возражение</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>«Я всё это уже понимаю»</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Логика поняла, а вина встроена глубже, чем логика достаёт</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>«понимает всё, продолжает сквозь зубы» (kanon §11)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Дальше — по одной строке на связку боль / желание / страх / возражение × продукт.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Аргумент ВСЕГДА через механику Виолы, со ссылкой на источник в базе.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Флагман / догрев</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>С5</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Боль (обида)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>«Обида разрушает нас, а он живёт и радуется»</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Прощение — снять обиду с себя, а не оправдать обидчика</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>письмо себе; чужое адресату (kanon §7, §8.2)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>«прости и забудь»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Догрев</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>С5</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Возражение</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>«Извинения без изменений — самый жестокий вид манипуляции»</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Речь не о том, простить ли его, а о том, чтобы освободить себя</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>прощение себя (kanon §8.2)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>оправдывать обидчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Лид-магнит</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>все</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Крючок (узнавание)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>«Стало легче на душе, сохраню, буду переслушивать, когда накроет»</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Вход = зеркало: назвать её ситуацию её словами, инструмент — после</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>подача (не «обучение»)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>«обучение» вместо узнавания</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Событие 1990</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>С3</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Боль</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>«Неловко назвать свою цену за работу»</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Право назвать цену — это «мне можно», не наглость</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ситуация 1 лид-магнита; Т3 (kanon §3, §7)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
